--- a/Game/Zone.xlsx
+++ b/Game/Zone.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="531">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">world</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252 Patch 2</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Ylva</t>
@@ -704,6 +704,15 @@
     <t xml:space="preserve">古城</t>
   </si>
   <si>
+    <t xml:space="preserve">oldchurch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old Church</t>
+  </si>
+  <si>
+    <t xml:space="preserve">古い教会</t>
+  </si>
+  <si>
     <t xml:space="preserve">keep_seeker</t>
   </si>
   <si>
@@ -1094,6 +1103,9 @@
     <t xml:space="preserve">演奏会場</t>
   </si>
   <si>
+    <t xml:space="preserve">instance_wedding</t>
+  </si>
+  <si>
     <t xml:space="preserve">dungeon</t>
   </si>
   <si>
@@ -1223,6 +1235,9 @@
     <t xml:space="preserve">Alpha 15.1</t>
   </si>
   <si>
+    <t xml:space="preserve">EA 23.281</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alpha 20.64</t>
   </si>
   <si>
@@ -1365,6 +1380,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thành Cổ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà thờ cũ</t>
   </si>
   <si>
     <t xml:space="preserve">Thành của Seeker</t>
@@ -1710,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -1722,7 +1740,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -1738,10 +1756,10 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C4" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D4" t="s">
         <v>18</v>
@@ -1750,7 +1768,7 @@
         <v>19</v>
       </c>
       <c r="F4" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="G4" t="s">
         <v>20</v>
@@ -1766,10 +1784,10 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C5" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -1787,10 +1805,10 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
@@ -1808,10 +1826,10 @@
         <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C7" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D7" t="s">
         <v>29</v>
@@ -1822,7 +1840,7 @@
       <c r="G7"/>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
@@ -1836,10 +1854,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C8" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -1857,7 +1875,7 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -1869,7 +1887,7 @@
         <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G9" t="s">
         <v>39</v>
@@ -1885,10 +1903,10 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D10" t="s">
         <v>42</v>
@@ -1906,7 +1924,7 @@
         <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C11" t="s">
         <v>45</v>
@@ -1927,10 +1945,10 @@
         <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D12" t="s">
         <v>48</v>
@@ -1948,10 +1966,10 @@
         <v>50</v>
       </c>
       <c r="B13" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C13" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D13" t="s">
         <v>51</v>
@@ -1960,7 +1978,7 @@
         <v>52</v>
       </c>
       <c r="F13" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="G13" t="s">
         <v>53</v>
@@ -1976,10 +1994,10 @@
         <v>55</v>
       </c>
       <c r="B14" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C14" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D14" t="s">
         <v>56</v>
@@ -1988,7 +2006,7 @@
         <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="G14" t="s">
         <v>58</v>
@@ -2004,7 +2022,7 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C15" t="s">
         <v>61</v>
@@ -2016,7 +2034,7 @@
         <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G15" t="s">
         <v>63</v>
@@ -2032,10 +2050,10 @@
         <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C16" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D16" t="s">
         <v>66</v>
@@ -2044,7 +2062,7 @@
         <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="G16" t="s">
         <v>68</v>
@@ -2060,10 +2078,10 @@
         <v>70</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C17" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -2081,10 +2099,10 @@
         <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C18" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D18" t="s">
         <v>51</v>
@@ -2093,7 +2111,7 @@
         <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="G18" t="s">
         <v>75</v>
@@ -2109,10 +2127,10 @@
         <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C19" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D19" t="s">
         <v>78</v>
@@ -2130,10 +2148,10 @@
         <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
@@ -2151,7 +2169,7 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C21" t="s">
         <v>84</v>
@@ -2172,7 +2190,7 @@
         <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C22" t="s">
         <v>87</v>
@@ -2193,10 +2211,10 @@
         <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C23" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D23" t="s">
         <v>90</v>
@@ -2214,10 +2232,10 @@
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C24" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -2235,10 +2253,10 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C25" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D25" t="s">
         <v>96</v>
@@ -2256,7 +2274,7 @@
         <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
         <v>99</v>
@@ -2270,7 +2288,7 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="J26" t="s">
         <v>101</v>
@@ -2284,7 +2302,7 @@
         <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C27" t="s">
         <v>104</v>
@@ -2298,7 +2316,7 @@
       <c r="G27"/>
       <c r="H27"/>
       <c r="I27" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="J27" t="s">
         <v>106</v>
@@ -2312,10 +2330,10 @@
         <v>108</v>
       </c>
       <c r="B28" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C28" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D28" t="s">
         <v>109</v>
@@ -2326,7 +2344,7 @@
       <c r="G28"/>
       <c r="H28"/>
       <c r="I28" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="J28" t="s">
         <v>111</v>
@@ -2340,10 +2358,10 @@
         <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D29" t="s">
         <v>114</v>
@@ -2361,10 +2379,10 @@
         <v>116</v>
       </c>
       <c r="B30" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C30" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D30" t="s">
         <v>117</v>
@@ -2382,10 +2400,10 @@
         <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C31" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
@@ -2396,7 +2414,7 @@
       <c r="G31"/>
       <c r="H31"/>
       <c r="I31" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="J31" t="s">
         <v>122</v>
@@ -2410,7 +2428,7 @@
         <v>124</v>
       </c>
       <c r="B32" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C32" t="s">
         <v>125</v>
@@ -2424,7 +2442,7 @@
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="J32" t="s">
         <v>127</v>
@@ -2438,10 +2456,10 @@
         <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C33" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D33" t="s">
         <v>130</v>
@@ -2459,10 +2477,10 @@
         <v>132</v>
       </c>
       <c r="B34" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C34" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="D34" t="s">
         <v>133</v>
@@ -2480,10 +2498,10 @@
         <v>135</v>
       </c>
       <c r="B35" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C35" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D35" t="s">
         <v>136</v>
@@ -2501,10 +2519,10 @@
         <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C36" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D36" t="s">
         <v>139</v>
@@ -2522,10 +2540,10 @@
         <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C37" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D37" t="s">
         <v>142</v>
@@ -2547,7 +2565,7 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C38" t="s">
         <v>147</v>
@@ -2561,7 +2579,7 @@
       <c r="G38"/>
       <c r="H38"/>
       <c r="I38" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="J38" t="s">
         <v>149</v>
@@ -2575,7 +2593,7 @@
         <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C39" t="s">
         <v>152</v>
@@ -2596,10 +2614,10 @@
         <v>154</v>
       </c>
       <c r="B40" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C40" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D40" t="s">
         <v>155</v>
@@ -2617,7 +2635,7 @@
         <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C41" t="s">
         <v>158</v>
@@ -2631,7 +2649,7 @@
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="J41" t="s">
         <v>160</v>
@@ -2645,7 +2663,7 @@
         <v>162</v>
       </c>
       <c r="B42" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C42" t="s">
         <v>163</v>
@@ -2659,7 +2677,7 @@
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="J42" t="s">
         <v>165</v>
@@ -2673,10 +2691,10 @@
         <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C43" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D43" t="s">
         <v>168</v>
@@ -2687,7 +2705,7 @@
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="J43" t="s">
         <v>170</v>
@@ -2701,10 +2719,10 @@
         <v>172</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C44" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D44" t="s">
         <v>173</v>
@@ -2715,7 +2733,7 @@
       <c r="G44"/>
       <c r="H44"/>
       <c r="I44" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="J44" t="s">
         <v>175</v>
@@ -2729,10 +2747,10 @@
         <v>177</v>
       </c>
       <c r="B45" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C45" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="D45" t="s">
         <v>178</v>
@@ -2743,7 +2761,7 @@
       <c r="G45"/>
       <c r="H45"/>
       <c r="I45" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="J45" t="s">
         <v>180</v>
@@ -2757,10 +2775,10 @@
         <v>182</v>
       </c>
       <c r="B46" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C46" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D46" t="s">
         <v>183</v>
@@ -2771,7 +2789,7 @@
       <c r="G46"/>
       <c r="H46"/>
       <c r="I46" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="J46" t="s">
         <v>185</v>
@@ -2785,7 +2803,7 @@
         <v>187</v>
       </c>
       <c r="B47" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C47" t="s">
         <v>188</v>
@@ -2799,7 +2817,7 @@
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="J47" t="s">
         <v>190</v>
@@ -2813,7 +2831,7 @@
         <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C48" t="s">
         <v>193</v>
@@ -2827,7 +2845,7 @@
       <c r="G48"/>
       <c r="H48"/>
       <c r="I48" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="J48" t="s">
         <v>195</v>
@@ -2841,7 +2859,7 @@
         <v>197</v>
       </c>
       <c r="B49" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C49" t="s">
         <v>198</v>
@@ -2855,7 +2873,7 @@
       <c r="G49"/>
       <c r="H49"/>
       <c r="I49" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="J49" t="s">
         <v>200</v>
@@ -2869,7 +2887,7 @@
         <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C50" t="s">
         <v>203</v>
@@ -2883,7 +2901,7 @@
       <c r="G50"/>
       <c r="H50"/>
       <c r="I50" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="J50" t="s">
         <v>205</v>
@@ -2897,10 +2915,10 @@
         <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="D51" t="s">
         <v>208</v>
@@ -2918,7 +2936,7 @@
         <v>210</v>
       </c>
       <c r="B52" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C52" t="s">
         <v>211</v>
@@ -2932,7 +2950,7 @@
       <c r="G52"/>
       <c r="H52"/>
       <c r="I52" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="J52" t="s">
         <v>213</v>
@@ -2946,10 +2964,10 @@
         <v>215</v>
       </c>
       <c r="B53" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C53" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D53" t="s">
         <v>216</v>
@@ -2967,10 +2985,10 @@
         <v>218</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C54" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D54" t="s">
         <v>219</v>
@@ -2988,10 +3006,10 @@
         <v>221</v>
       </c>
       <c r="B55" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C55" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="D55" t="s">
         <v>222</v>
@@ -3002,7 +3020,7 @@
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="J55" t="s">
         <v>224</v>
@@ -3016,10 +3034,10 @@
         <v>226</v>
       </c>
       <c r="B56" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C56" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="D56" t="s">
         <v>227</v>
@@ -3037,10 +3055,10 @@
         <v>229</v>
       </c>
       <c r="B57" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C57" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D57" t="s">
         <v>230</v>
@@ -3058,10 +3076,10 @@
         <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>390</v>
+        <v>407</v>
       </c>
       <c r="C58" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="D58" t="s">
         <v>233</v>
@@ -3071,43 +3089,43 @@
       </c>
       <c r="G58"/>
       <c r="H58"/>
-      <c r="J58" t="s">
-        <v>235</v>
-      </c>
-      <c r="K58" t="s">
-        <v>236</v>
-      </c>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>235</v>
+      </c>
+      <c r="B59" t="s">
+        <v>394</v>
+      </c>
+      <c r="C59" t="s">
+        <v>457</v>
+      </c>
+      <c r="D59" t="s">
+        <v>236</v>
+      </c>
+      <c r="E59" t="s">
         <v>237</v>
-      </c>
-      <c r="B59" t="s">
-        <v>390</v>
-      </c>
-      <c r="C59" t="s">
-        <v>452</v>
-      </c>
-      <c r="D59" t="s">
-        <v>238</v>
-      </c>
-      <c r="E59" t="s">
-        <v>239</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
-      <c r="J59"/>
-      <c r="K59"/>
+      <c r="J59" t="s">
+        <v>238</v>
+      </c>
+      <c r="K59" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
         <v>240</v>
       </c>
       <c r="B60" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C60" t="s">
-        <v>241</v>
+        <v>458</v>
       </c>
       <c r="D60" t="s">
         <v>241</v>
@@ -3125,10 +3143,10 @@
         <v>243</v>
       </c>
       <c r="B61" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C61" t="s">
-        <v>453</v>
+        <v>244</v>
       </c>
       <c r="D61" t="s">
         <v>244</v>
@@ -3146,10 +3164,10 @@
         <v>246</v>
       </c>
       <c r="B62" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D62" t="s">
         <v>247</v>
@@ -3159,124 +3177,124 @@
       </c>
       <c r="G62"/>
       <c r="H62"/>
-      <c r="I62" t="s">
-        <v>515</v>
-      </c>
-      <c r="J62" t="s">
-        <v>249</v>
-      </c>
-      <c r="K62" t="s">
-        <v>250</v>
-      </c>
+      <c r="J62"/>
+      <c r="K62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>249</v>
+      </c>
+      <c r="B63" t="s">
+        <v>408</v>
+      </c>
+      <c r="C63" t="s">
+        <v>460</v>
+      </c>
+      <c r="D63" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" t="s">
         <v>251</v>
-      </c>
-      <c r="B63" t="s">
-        <v>390</v>
-      </c>
-      <c r="C63" t="s">
-        <v>455</v>
-      </c>
-      <c r="D63" t="s">
-        <v>252</v>
-      </c>
-      <c r="E63" t="s">
-        <v>253</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="J63" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K63" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>254</v>
+      </c>
+      <c r="B64" t="s">
+        <v>394</v>
+      </c>
+      <c r="C64" t="s">
+        <v>461</v>
+      </c>
+      <c r="D64" t="s">
+        <v>255</v>
+      </c>
+      <c r="E64" t="s">
         <v>256</v>
-      </c>
-      <c r="B64" t="s">
-        <v>390</v>
-      </c>
-      <c r="C64" t="s">
-        <v>456</v>
-      </c>
-      <c r="D64" t="s">
-        <v>257</v>
-      </c>
-      <c r="E64" t="s">
-        <v>258</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
+      <c r="I64" t="s">
+        <v>522</v>
+      </c>
       <c r="J64" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K64" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>259</v>
+      </c>
+      <c r="B65" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" t="s">
+        <v>462</v>
+      </c>
+      <c r="D65" t="s">
+        <v>260</v>
+      </c>
+      <c r="E65" t="s">
         <v>261</v>
-      </c>
-      <c r="B65" t="s">
-        <v>390</v>
-      </c>
-      <c r="C65" t="s">
-        <v>457</v>
-      </c>
-      <c r="D65" t="s">
-        <v>262</v>
-      </c>
-      <c r="E65" t="s">
-        <v>263</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
       <c r="J65" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K65" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>264</v>
+      </c>
+      <c r="B66" t="s">
+        <v>394</v>
+      </c>
+      <c r="C66" t="s">
+        <v>463</v>
+      </c>
+      <c r="D66" t="s">
+        <v>265</v>
+      </c>
+      <c r="E66" t="s">
         <v>266</v>
-      </c>
-      <c r="B66" t="s">
-        <v>396</v>
-      </c>
-      <c r="C66" t="s">
-        <v>458</v>
-      </c>
-      <c r="D66" t="s">
-        <v>267</v>
-      </c>
-      <c r="E66" t="s">
-        <v>268</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
-      <c r="J66"/>
-      <c r="K66"/>
+      <c r="J66" t="s">
+        <v>267</v>
+      </c>
+      <c r="K66" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
         <v>269</v>
       </c>
       <c r="B67" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C67" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D67" t="s">
         <v>270</v>
@@ -3286,99 +3304,99 @@
       </c>
       <c r="G67"/>
       <c r="H67"/>
-      <c r="J67" t="s">
-        <v>272</v>
-      </c>
-      <c r="K67" t="s">
-        <v>273</v>
-      </c>
+      <c r="J67"/>
+      <c r="K67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>272</v>
+      </c>
+      <c r="B68" t="s">
+        <v>409</v>
+      </c>
+      <c r="C68" t="s">
+        <v>465</v>
+      </c>
+      <c r="D68" t="s">
+        <v>273</v>
+      </c>
+      <c r="E68" t="s">
         <v>274</v>
-      </c>
-      <c r="B68" t="s">
-        <v>390</v>
-      </c>
-      <c r="C68" t="s">
-        <v>275</v>
-      </c>
-      <c r="D68" t="s">
-        <v>275</v>
-      </c>
-      <c r="E68" t="s">
-        <v>276</v>
       </c>
       <c r="G68"/>
       <c r="H68"/>
-      <c r="I68" t="s">
-        <v>517</v>
-      </c>
       <c r="J68" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K68" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
+        <v>277</v>
+      </c>
+      <c r="B69" t="s">
+        <v>394</v>
+      </c>
+      <c r="C69" t="s">
+        <v>278</v>
+      </c>
+      <c r="D69" t="s">
+        <v>278</v>
+      </c>
+      <c r="E69" t="s">
         <v>279</v>
-      </c>
-      <c r="B69" t="s">
-        <v>390</v>
-      </c>
-      <c r="C69" t="s">
-        <v>460</v>
-      </c>
-      <c r="D69" t="s">
-        <v>280</v>
-      </c>
-      <c r="E69" t="s">
-        <v>281</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
       <c r="I69" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="J69" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K69" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>282</v>
+      </c>
+      <c r="B70" t="s">
+        <v>394</v>
+      </c>
+      <c r="C70" t="s">
+        <v>466</v>
+      </c>
+      <c r="D70" t="s">
+        <v>283</v>
+      </c>
+      <c r="E70" t="s">
         <v>284</v>
-      </c>
-      <c r="B70" t="s">
-        <v>393</v>
-      </c>
-      <c r="C70" t="s">
-        <v>461</v>
-      </c>
-      <c r="D70" t="s">
-        <v>285</v>
-      </c>
-      <c r="E70" t="s">
-        <v>286</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
-      <c r="J70"/>
-      <c r="K70"/>
+      <c r="I70" t="s">
+        <v>524</v>
+      </c>
+      <c r="J70" t="s">
+        <v>285</v>
+      </c>
+      <c r="K70" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
         <v>287</v>
       </c>
       <c r="B71" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C71" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D71" t="s">
         <v>288</v>
@@ -3396,10 +3414,10 @@
         <v>290</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="C72" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D72" t="s">
         <v>291</v>
@@ -3409,46 +3427,46 @@
       </c>
       <c r="G72"/>
       <c r="H72"/>
-      <c r="I72" t="s">
-        <v>519</v>
-      </c>
-      <c r="J72" t="s">
-        <v>293</v>
-      </c>
-      <c r="K72" t="s">
-        <v>294</v>
-      </c>
+      <c r="J72"/>
+      <c r="K72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" t="s">
+        <v>394</v>
+      </c>
+      <c r="C73" t="s">
+        <v>469</v>
+      </c>
+      <c r="D73" t="s">
+        <v>294</v>
+      </c>
+      <c r="E73" t="s">
         <v>295</v>
-      </c>
-      <c r="B73" t="s">
-        <v>390</v>
-      </c>
-      <c r="C73" t="s">
-        <v>464</v>
-      </c>
-      <c r="D73" t="s">
-        <v>296</v>
-      </c>
-      <c r="E73" t="s">
-        <v>297</v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
-      <c r="J73"/>
-      <c r="K73"/>
+      <c r="I73" t="s">
+        <v>525</v>
+      </c>
+      <c r="J73" t="s">
+        <v>296</v>
+      </c>
+      <c r="K73" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
         <v>298</v>
       </c>
       <c r="B74" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="C74" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D74" t="s">
         <v>299</v>
@@ -3458,201 +3476,201 @@
       </c>
       <c r="G74"/>
       <c r="H74"/>
-      <c r="I74" t="s">
-        <v>520</v>
-      </c>
-      <c r="J74" t="s">
-        <v>301</v>
-      </c>
-      <c r="K74" t="s">
-        <v>302</v>
-      </c>
+      <c r="J74"/>
+      <c r="K74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" t="s">
+        <v>410</v>
+      </c>
+      <c r="C75" t="s">
+        <v>471</v>
+      </c>
+      <c r="D75" t="s">
+        <v>302</v>
+      </c>
+      <c r="E75" t="s">
         <v>303</v>
-      </c>
-      <c r="B75" t="s">
-        <v>405</v>
-      </c>
-      <c r="C75" t="s">
-        <v>466</v>
-      </c>
-      <c r="D75" t="s">
-        <v>304</v>
-      </c>
-      <c r="E75" t="s">
-        <v>305</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="J75" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K75" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>306</v>
+      </c>
+      <c r="B76" t="s">
+        <v>410</v>
+      </c>
+      <c r="C76" t="s">
+        <v>472</v>
+      </c>
+      <c r="D76" t="s">
+        <v>307</v>
+      </c>
+      <c r="E76" t="s">
         <v>308</v>
-      </c>
-      <c r="B76" t="s">
-        <v>405</v>
-      </c>
-      <c r="C76" t="s">
-        <v>466</v>
-      </c>
-      <c r="D76" t="s">
-        <v>304</v>
-      </c>
-      <c r="E76" t="s">
-        <v>305</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
-      <c r="J76"/>
-      <c r="K76"/>
+      <c r="I76" t="s">
+        <v>527</v>
+      </c>
+      <c r="J76" t="s">
+        <v>309</v>
+      </c>
+      <c r="K76" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B77" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="C77" t="s">
-        <v>310</v>
+        <v>472</v>
       </c>
       <c r="D77" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E77" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
-      <c r="I77" t="s">
-        <v>522</v>
-      </c>
-      <c r="J77" t="s">
-        <v>312</v>
-      </c>
-      <c r="K77" t="s">
-        <v>313</v>
-      </c>
+      <c r="J77"/>
+      <c r="K77"/>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>312</v>
+      </c>
+      <c r="B78" t="s">
+        <v>394</v>
+      </c>
+      <c r="C78" t="s">
+        <v>313</v>
+      </c>
+      <c r="D78" t="s">
+        <v>313</v>
+      </c>
+      <c r="E78" t="s">
         <v>314</v>
-      </c>
-      <c r="B78" t="s">
-        <v>406</v>
-      </c>
-      <c r="C78" t="s">
-        <v>467</v>
-      </c>
-      <c r="D78" t="s">
-        <v>315</v>
-      </c>
-      <c r="E78" t="s">
-        <v>316</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
+      <c r="I78" t="s">
+        <v>528</v>
+      </c>
       <c r="J78" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K78" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>317</v>
+      </c>
+      <c r="B79" t="s">
+        <v>411</v>
+      </c>
+      <c r="C79" t="s">
+        <v>473</v>
+      </c>
+      <c r="D79" t="s">
+        <v>318</v>
+      </c>
+      <c r="E79" t="s">
         <v>319</v>
-      </c>
-      <c r="B79" t="s">
-        <v>399</v>
-      </c>
-      <c r="C79" t="s">
-        <v>468</v>
-      </c>
-      <c r="D79" t="s">
-        <v>320</v>
-      </c>
-      <c r="E79" t="s">
-        <v>321</v>
       </c>
       <c r="G79"/>
       <c r="H79"/>
       <c r="J79" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="K79" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>322</v>
+      </c>
+      <c r="B80" t="s">
+        <v>403</v>
+      </c>
+      <c r="C80" t="s">
+        <v>474</v>
+      </c>
+      <c r="D80" t="s">
+        <v>323</v>
+      </c>
+      <c r="E80" t="s">
         <v>324</v>
-      </c>
-      <c r="B80" t="s">
-        <v>390</v>
-      </c>
-      <c r="C80" t="s">
-        <v>469</v>
-      </c>
-      <c r="D80" t="s">
-        <v>325</v>
-      </c>
-      <c r="E80" t="s">
-        <v>326</v>
       </c>
       <c r="G80"/>
       <c r="H80"/>
-      <c r="I80" t="s">
-        <v>523</v>
-      </c>
       <c r="J80" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K80" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>327</v>
+      </c>
+      <c r="B81" t="s">
+        <v>394</v>
+      </c>
+      <c r="C81" t="s">
+        <v>475</v>
+      </c>
+      <c r="D81" t="s">
+        <v>328</v>
+      </c>
+      <c r="E81" t="s">
         <v>329</v>
-      </c>
-      <c r="B81" t="s">
-        <v>390</v>
-      </c>
-      <c r="C81" t="s">
-        <v>470</v>
-      </c>
-      <c r="D81" t="s">
-        <v>330</v>
-      </c>
-      <c r="E81" t="s">
-        <v>331</v>
       </c>
       <c r="G81"/>
       <c r="H81"/>
-      <c r="J81"/>
-      <c r="K81"/>
+      <c r="I81" t="s">
+        <v>529</v>
+      </c>
+      <c r="J81" t="s">
+        <v>330</v>
+      </c>
+      <c r="K81" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
         <v>332</v>
       </c>
       <c r="B82" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C82" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="D82" t="s">
         <v>333</v>
@@ -3670,16 +3688,16 @@
         <v>335</v>
       </c>
       <c r="B83" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C83" t="s">
-        <v>99</v>
+        <v>477</v>
       </c>
       <c r="D83" t="s">
-        <v>99</v>
+        <v>336</v>
       </c>
       <c r="E83" t="s">
-        <v>100</v>
+        <v>337</v>
       </c>
       <c r="G83"/>
       <c r="H83"/>
@@ -3688,10 +3706,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C84" t="s">
         <v>99</v>
@@ -3709,19 +3727,19 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C85" t="s">
-        <v>472</v>
+        <v>99</v>
       </c>
       <c r="D85" t="s">
-        <v>338</v>
+        <v>99</v>
       </c>
       <c r="E85" t="s">
-        <v>339</v>
+        <v>100</v>
       </c>
       <c r="G85"/>
       <c r="H85"/>
@@ -3733,16 +3751,16 @@
         <v>340</v>
       </c>
       <c r="B86" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="C86" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D86" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E86" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="G86"/>
       <c r="H86"/>
@@ -3751,19 +3769,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>343</v>
+      </c>
+      <c r="B87" t="s">
+        <v>412</v>
+      </c>
+      <c r="C87" t="s">
+        <v>478</v>
+      </c>
+      <c r="D87" t="s">
         <v>341</v>
       </c>
-      <c r="B87" t="s">
-        <v>408</v>
-      </c>
-      <c r="C87" t="s">
+      <c r="E87" t="s">
         <v>342</v>
-      </c>
-      <c r="D87" t="s">
-        <v>342</v>
-      </c>
-      <c r="E87" t="s">
-        <v>343</v>
       </c>
       <c r="G87"/>
       <c r="H87"/>
@@ -3775,10 +3793,10 @@
         <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C88" t="s">
-        <v>473</v>
+        <v>345</v>
       </c>
       <c r="D88" t="s">
         <v>345</v>
@@ -3796,10 +3814,10 @@
         <v>347</v>
       </c>
       <c r="B89" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="C89" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D89" t="s">
         <v>348</v>
@@ -3817,10 +3835,10 @@
         <v>350</v>
       </c>
       <c r="B90" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C90" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D90" t="s">
         <v>351</v>
@@ -3838,10 +3856,10 @@
         <v>353</v>
       </c>
       <c r="B91" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C91" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D91" t="s">
         <v>354</v>
@@ -3859,10 +3877,10 @@
         <v>356</v>
       </c>
       <c r="B92" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C92" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="D92" t="s">
         <v>357</v>
@@ -3880,10 +3898,10 @@
         <v>359</v>
       </c>
       <c r="B93" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C93" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D93" t="s">
         <v>360</v>
@@ -3901,16 +3919,16 @@
         <v>362</v>
       </c>
       <c r="B94" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C94" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="D94" t="s">
-        <v>363</v>
+        <v>230</v>
       </c>
       <c r="E94" t="s">
-        <v>364</v>
+        <v>231</v>
       </c>
       <c r="G94"/>
       <c r="H94"/>
@@ -3919,19 +3937,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>363</v>
+      </c>
+      <c r="B95" t="s">
+        <v>405</v>
+      </c>
+      <c r="C95" t="s">
+        <v>484</v>
+      </c>
+      <c r="D95" t="s">
+        <v>364</v>
+      </c>
+      <c r="E95" t="s">
         <v>365</v>
-      </c>
-      <c r="B95" t="s">
-        <v>410</v>
-      </c>
-      <c r="C95" t="s">
-        <v>480</v>
-      </c>
-      <c r="D95" t="s">
-        <v>366</v>
-      </c>
-      <c r="E95" t="s">
-        <v>367</v>
       </c>
       <c r="G95"/>
       <c r="H95"/>
@@ -3940,19 +3958,19 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
+        <v>366</v>
+      </c>
+      <c r="B96" t="s">
+        <v>415</v>
+      </c>
+      <c r="C96" t="s">
+        <v>485</v>
+      </c>
+      <c r="D96" t="s">
+        <v>367</v>
+      </c>
+      <c r="E96" t="s">
         <v>368</v>
-      </c>
-      <c r="B96" t="s">
-        <v>401</v>
-      </c>
-      <c r="C96" t="s">
-        <v>481</v>
-      </c>
-      <c r="D96" t="s">
-        <v>369</v>
-      </c>
-      <c r="E96" t="s">
-        <v>370</v>
       </c>
       <c r="G96"/>
       <c r="H96"/>
@@ -3961,19 +3979,19 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
+        <v>369</v>
+      </c>
+      <c r="B97" t="s">
+        <v>415</v>
+      </c>
+      <c r="C97" t="s">
+        <v>486</v>
+      </c>
+      <c r="D97" t="s">
+        <v>370</v>
+      </c>
+      <c r="E97" t="s">
         <v>371</v>
-      </c>
-      <c r="B97" t="s">
-        <v>401</v>
-      </c>
-      <c r="C97" t="s">
-        <v>482</v>
-      </c>
-      <c r="D97" t="s">
-        <v>372</v>
-      </c>
-      <c r="E97" t="s">
-        <v>373</v>
       </c>
       <c r="G97"/>
       <c r="H97"/>
@@ -3982,19 +4000,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
+        <v>372</v>
+      </c>
+      <c r="B98" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" t="s">
+        <v>487</v>
+      </c>
+      <c r="D98" t="s">
+        <v>373</v>
+      </c>
+      <c r="E98" t="s">
         <v>374</v>
-      </c>
-      <c r="B98" t="s">
-        <v>404</v>
-      </c>
-      <c r="C98" t="s">
-        <v>483</v>
-      </c>
-      <c r="D98" t="s">
-        <v>375</v>
-      </c>
-      <c r="E98" t="s">
-        <v>376</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
@@ -4003,19 +4021,19 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>375</v>
+      </c>
+      <c r="B99" t="s">
+        <v>405</v>
+      </c>
+      <c r="C99" t="s">
+        <v>488</v>
+      </c>
+      <c r="D99" t="s">
+        <v>376</v>
+      </c>
+      <c r="E99" t="s">
         <v>377</v>
-      </c>
-      <c r="B99" t="s">
-        <v>411</v>
-      </c>
-      <c r="C99" t="s">
-        <v>484</v>
-      </c>
-      <c r="D99" t="s">
-        <v>378</v>
-      </c>
-      <c r="E99" t="s">
-        <v>379</v>
       </c>
       <c r="G99"/>
       <c r="H99"/>
@@ -4024,19 +4042,19 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
+        <v>378</v>
+      </c>
+      <c r="B100" t="s">
+        <v>409</v>
+      </c>
+      <c r="C100" t="s">
+        <v>489</v>
+      </c>
+      <c r="D100" t="s">
+        <v>379</v>
+      </c>
+      <c r="E100" t="s">
         <v>380</v>
-      </c>
-      <c r="B100" t="s">
-        <v>390</v>
-      </c>
-      <c r="C100" t="s">
-        <v>485</v>
-      </c>
-      <c r="D100" t="s">
-        <v>381</v>
-      </c>
-      <c r="E100" t="s">
-        <v>382</v>
       </c>
       <c r="G100"/>
       <c r="H100"/>
@@ -4045,19 +4063,19 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>381</v>
+      </c>
+      <c r="B101" t="s">
+        <v>416</v>
+      </c>
+      <c r="C101" t="s">
+        <v>490</v>
+      </c>
+      <c r="D101" t="s">
+        <v>382</v>
+      </c>
+      <c r="E101" t="s">
         <v>383</v>
-      </c>
-      <c r="B101" t="s">
-        <v>412</v>
-      </c>
-      <c r="C101" t="s">
-        <v>486</v>
-      </c>
-      <c r="D101" t="s">
-        <v>384</v>
-      </c>
-      <c r="E101" t="s">
-        <v>352</v>
       </c>
       <c r="G101"/>
       <c r="H101"/>
@@ -4066,30 +4084,72 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
+        <v>384</v>
+      </c>
+      <c r="B102" t="s">
+        <v>394</v>
+      </c>
+      <c r="C102" t="s">
+        <v>491</v>
+      </c>
+      <c r="D102" t="s">
         <v>385</v>
       </c>
-      <c r="B102" t="s">
-        <v>413</v>
-      </c>
-      <c r="C102" t="s">
-        <v>487</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>386</v>
-      </c>
-      <c r="E102" t="s">
-        <v>387</v>
       </c>
       <c r="G102"/>
       <c r="H102"/>
-      <c r="I102" t="s">
-        <v>524</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="J102"/>
+      <c r="K102"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>387</v>
+      </c>
+      <c r="B103" t="s">
+        <v>417</v>
+      </c>
+      <c r="C103" t="s">
+        <v>492</v>
+      </c>
+      <c r="D103" t="s">
         <v>388</v>
       </c>
-      <c r="K102" t="s">
+      <c r="E103" t="s">
+        <v>355</v>
+      </c>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
         <v>389</v>
+      </c>
+      <c r="B104" t="s">
+        <v>418</v>
+      </c>
+      <c r="C104" t="s">
+        <v>493</v>
+      </c>
+      <c r="D104" t="s">
+        <v>390</v>
+      </c>
+      <c r="E104" t="s">
+        <v>391</v>
+      </c>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104" t="s">
+        <v>530</v>
+      </c>
+      <c r="J104" t="s">
+        <v>392</v>
+      </c>
+      <c r="K104" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>
